--- a/artfynd/A 33116-2026 artfynd.xlsx
+++ b/artfynd/A 33116-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>119219910</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33116-2026 artfynd.xlsx
+++ b/artfynd/A 33116-2026 artfynd.xlsx
@@ -811,11 +811,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnemyrfjället, Dls</t>

--- a/artfynd/A 33116-2026 artfynd.xlsx
+++ b/artfynd/A 33116-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>119219910</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
